--- a/backend/data/financials_by_company/1D3.F.xlsx
+++ b/backend/data/financials_by_company/1D3.F.xlsx
@@ -3320,222 +3320,222 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>financialCurrency</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>sharesOutstanding</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>impliedSharesOutstanding</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>bookValue</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>marketCap</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="BD1" t="inlineStr">
-        <is>
-          <t>financialCurrency</t>
-        </is>
-      </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="BG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="BH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="BK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>sharesOutstanding</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>impliedSharesOutstanding</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>bookValue</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>marketCap</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
@@ -3552,28 +3552,28 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="K2" t="n">
         <v>700</v>
@@ -3591,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
         <v>2</v>
@@ -3609,10 +3609,10 @@
         <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2268</v>
+        <v>2.2236</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8388</v>
+        <v>2.7702</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -3666,163 +3666,163 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="AJ2" t="b">
+      <c r="AJ2" t="n">
+        <v>0.8695644</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>finmb_290103394</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="AR2" t="b">
         <v>0</v>
       </c>
-      <c r="AK2" t="b">
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2.32 - 2.32</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AY2" t="n">
+        <v>0.31999993</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.15999997</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2.0 - 3.82</t>
+        </is>
+      </c>
+      <c r="BB2" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-0.39267015</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-10.15625</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1778821200</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1786597200</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1786597200</v>
+      </c>
+      <c r="BH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>56324607</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>56324607</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>4.641269</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.09640002</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.043353133</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>-0.45020008</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>-0.16251537</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>130673088</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>0.49986327</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
         <v>1594274400000</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.1400001</v>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>2.2 - 2.4</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BY2" t="n">
+        <v>1782108602</v>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>Seritage Growth Properties    R</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
         <is>
           <t>Seritage Growth Properties</t>
         </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.2500043</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>1780430102</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>finmb_290103394</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>Seritage Growth Properties    R</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.3800001</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.19000006</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2.0 - 3.82</t>
-        </is>
-      </c>
-      <c r="BI2" t="n">
-        <v>-1.4399998</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-0.37696332</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>-8.943087</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1778821200</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1786597200</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1786597200</v>
-      </c>
-      <c r="BO2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>-1.24</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>56324607</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>56324607</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>4.5766354</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0.15320015</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.06879834</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>-0.45879984</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>-0.16161753</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>134052576</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0.5200327</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>15</v>
       </c>
       <c r="CB2" t="inlineStr"/>
     </row>
